--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -43927,12 +43927,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -43966,81 +43966,100 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="O234" t="n">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="R234" t="n">
-        <v>1.116842958734282</v>
+        <v>3.681882888743638</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44067,17 +44086,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44111,81 +44130,175 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>5043</v>
+        <v>394</v>
       </c>
       <c r="O235" t="n">
-        <v>5043</v>
-      </c>
-      <c r="R235" t="n">
-        <v>1.444838730355601</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>394</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44217,12 +44330,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44247,7 +44360,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -44256,13 +44369,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>5051</v>
+        <v>257</v>
       </c>
       <c r="O236" t="n">
-        <v>5051</v>
+        <v>257</v>
       </c>
       <c r="R236" t="n">
-        <v>1.447130760861817</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -44295,42 +44408,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44392,7 +44505,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -44401,13 +44514,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>4835</v>
+        <v>5043</v>
       </c>
       <c r="O237" t="n">
-        <v>4835</v>
+        <v>5043</v>
       </c>
       <c r="R237" t="n">
-        <v>1.385245937193998</v>
+        <v>1.444838730355601</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44537,7 +44650,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -44546,13 +44659,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>4565</v>
+        <v>5051</v>
       </c>
       <c r="O238" t="n">
-        <v>4565</v>
+        <v>5051</v>
       </c>
       <c r="R238" t="n">
-        <v>1.307889907609225</v>
+        <v>1.447130760861817</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -44682,7 +44795,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -44691,13 +44804,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>5538</v>
+        <v>4835</v>
       </c>
       <c r="O239" t="n">
-        <v>5538</v>
+        <v>4835</v>
       </c>
       <c r="R239" t="n">
-        <v>1.586658117927686</v>
+        <v>1.385245937193998</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44797,12 +44910,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44827,109 +44940,90 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>8</v>
+        <v>4565</v>
       </c>
       <c r="O240" t="n">
-        <v>8</v>
+        <v>4565</v>
       </c>
       <c r="R240" t="n">
-        <v>0.142304733669131</v>
+        <v>1.307889907609225</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44956,17 +45050,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -44991,184 +45085,90 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>8</v>
+        <v>5538</v>
       </c>
       <c r="O241" t="n">
-        <v>8</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
+        <v>5538</v>
+      </c>
+      <c r="R241" t="n">
+        <v>1.586658117927686</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45200,12 +45200,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45239,13 +45239,13 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O242" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R242" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -45274,7 +45274,7 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -45292,47 +45292,47 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45364,12 +45364,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45403,29 +45403,29 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O243" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y243" t="inlineStr">
@@ -45450,7 +45450,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -45485,17 +45485,17 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -45513,7 +45513,7 @@
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
@@ -45523,7 +45523,7 @@
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT243" t="n">
@@ -45531,45 +45531,448 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>2</v>
+      </c>
+      <c r="O244" t="n">
+        <v>2</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV243" t="inlineStr">
+      <c r="AV244" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW243" t="inlineStr">
+      <c r="AW244" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX243" t="inlineStr">
+      <c r="AX244" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY243" t="inlineStr">
+      <c r="AY244" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ243" t="inlineStr">
+      <c r="AZ244" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA243" t="inlineStr">
+      <c r="BA244" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB243" t="inlineStr">
+      <c r="BB244" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC243" t="inlineStr">
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>2</v>
+      </c>
+      <c r="O245" t="n">
+        <v>2</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -45691,7 +46094,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -45701,7 +46104,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -45721,7 +46124,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -45753,7 +46156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263907</v>
+        <v>264307</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -45239,13 +45239,13 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O242" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R242" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -45403,10 +45403,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O243" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264307</v>
+        <v>264313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -43563,13 +43563,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="O232" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="R232" t="n">
-        <v>4.917752795711507</v>
+        <v>5.130029894806968</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -43727,10 +43727,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="O233" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -43966,13 +43966,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O234" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R234" t="n">
-        <v>3.681882888743638</v>
+        <v>3.672538008315355</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -44130,10 +44130,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O235" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -45239,13 +45239,13 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="O242" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="R242" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.5870070263851653</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -45403,10 +45403,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="O243" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -45642,13 +45642,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="O244" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R244" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.9375571876716183</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -45806,10 +45806,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264313</v>
+        <v>264388</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -43121,12 +43121,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43160,100 +43160,84 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>177</v>
+        <v>14059</v>
       </c>
       <c r="O230" t="n">
-        <v>177</v>
+        <v>14059</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>3.148492232429523</v>
+        <v>0.9950357289540184</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -43280,7 +43264,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -43324,103 +43308,28 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O231" t="n">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="R231" t="n">
+        <v>3.184068415846806</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -43519,17 +43428,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43563,22 +43472,39 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="O232" t="n">
-        <v>290</v>
-      </c>
-      <c r="R232" t="n">
-        <v>5.130029894806968</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>179</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -43586,6 +43512,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43598,7 +43582,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
@@ -43608,7 +43592,7 @@
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT232" t="n">
@@ -43616,47 +43600,47 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43683,7 +43667,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -43732,98 +43716,23 @@
       <c r="O233" t="n">
         <v>290</v>
       </c>
+      <c r="R233" t="n">
+        <v>5.130029894806968</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U233" t="inlineStr">
         <is>
           <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -43922,17 +43831,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -43966,22 +43875,39 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="O234" t="n">
-        <v>393</v>
-      </c>
-      <c r="R234" t="n">
-        <v>3.672538008315355</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>290</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -43989,6 +43915,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44011,7 +43995,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -44024,42 +44008,42 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44086,7 +44070,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -44135,98 +44119,23 @@
       <c r="O235" t="n">
         <v>393</v>
       </c>
+      <c r="R235" t="n">
+        <v>3.672538008315355</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Gonorré</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -44325,17 +44234,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44369,81 +44278,175 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>257</v>
+        <v>393</v>
       </c>
       <c r="O236" t="n">
-        <v>257</v>
-      </c>
-      <c r="R236" t="n">
-        <v>1.116842958734282</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>393</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44475,12 +44478,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44514,13 +44517,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>5043</v>
+        <v>257</v>
       </c>
       <c r="O237" t="n">
-        <v>5043</v>
+        <v>257</v>
       </c>
       <c r="R237" t="n">
-        <v>1.444838730355601</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44553,42 +44556,42 @@
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44650,7 +44653,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -44659,13 +44662,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>5051</v>
+        <v>5043</v>
       </c>
       <c r="O238" t="n">
-        <v>5051</v>
+        <v>5043</v>
       </c>
       <c r="R238" t="n">
-        <v>1.447130760861817</v>
+        <v>1.444838730355601</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -44795,7 +44798,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -44804,13 +44807,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>4835</v>
+        <v>5051</v>
       </c>
       <c r="O239" t="n">
-        <v>4835</v>
+        <v>5051</v>
       </c>
       <c r="R239" t="n">
-        <v>1.385245937193998</v>
+        <v>1.447130760861817</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44940,7 +44943,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -44949,13 +44952,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>4565</v>
+        <v>4835</v>
       </c>
       <c r="O240" t="n">
-        <v>4565</v>
+        <v>4835</v>
       </c>
       <c r="R240" t="n">
-        <v>1.307889907609225</v>
+        <v>1.385245937193998</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -45085,7 +45088,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -45094,13 +45097,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>5538</v>
+        <v>4565</v>
       </c>
       <c r="O241" t="n">
-        <v>5538</v>
+        <v>4565</v>
       </c>
       <c r="R241" t="n">
-        <v>1.586658117927686</v>
+        <v>1.307889907609225</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -45200,12 +45203,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45230,109 +45233,90 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>33</v>
+        <v>5538</v>
       </c>
       <c r="O242" t="n">
-        <v>33</v>
+        <v>5538</v>
       </c>
       <c r="R242" t="n">
-        <v>0.5870070263851653</v>
+        <v>1.586658117927686</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45359,7 +45343,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -45403,103 +45387,28 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O243" t="n">
-        <v>33</v>
+        <v>45</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.8004641268888618</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -45598,17 +45507,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45642,22 +45551,39 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O244" t="n">
-        <v>53</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.9375571876716183</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45665,6 +45591,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45677,7 +45661,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -45687,7 +45671,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -45695,47 +45679,47 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45762,7 +45746,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -45811,98 +45795,23 @@
       <c r="O245" t="n">
         <v>53</v>
       </c>
+      <c r="R245" t="n">
+        <v>0.9375571876716183</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
@@ -45975,6 +45884,390 @@
       <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>53</v>
+      </c>
+      <c r="O246" t="n">
+        <v>53</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>5030</v>
+      </c>
+      <c r="O247" t="n">
+        <v>5030</v>
+      </c>
+      <c r="R247" t="n">
+        <v>1.441114180783001</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46011,7 +46304,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -46094,7 +46387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -46104,7 +46397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -46156,7 +46449,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264388</v>
+        <v>283491</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="O2" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="O3" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -19579,10 +19579,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="O103" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="O104" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -25546,10 +25546,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="O135" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -25702,10 +25702,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="O136" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -37959,12 +37959,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37998,84 +37998,92 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>13411</v>
+        <v>1255</v>
       </c>
       <c r="O202" t="n">
-        <v>13411</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.9491730678570554</v>
+        <v>1255</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38102,17 +38110,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -38146,14 +38154,39 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>505</v>
+        <v>1255</v>
       </c>
       <c r="O203" t="n">
-        <v>505</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>1255</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Gonorrhoea (All Types)</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -38161,6 +38194,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary gonorrhoea notifications across all reported types; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38168,7 +38259,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -38178,55 +38269,55 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38253,17 +38344,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38297,170 +38388,84 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>505</v>
+        <v>13411</v>
       </c>
       <c r="O204" t="n">
-        <v>505</v>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>淋病</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:CN-AH:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
+        <v>13411</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.9491730678570554</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38492,12 +38497,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38531,10 +38536,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>322</v>
+        <v>505</v>
       </c>
       <c r="O205" t="n">
-        <v>322</v>
+        <v>505</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -38606,7 +38611,7 @@
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
@@ -38643,12 +38648,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38682,10 +38687,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>322</v>
+        <v>505</v>
       </c>
       <c r="O206" t="n">
-        <v>322</v>
+        <v>505</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
@@ -38729,7 +38734,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -38840,7 +38845,7 @@
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
@@ -38877,12 +38882,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38916,10 +38921,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2729</v>
+        <v>322</v>
       </c>
       <c r="O207" t="n">
-        <v>2729</v>
+        <v>322</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -38991,7 +38996,7 @@
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
@@ -39028,12 +39033,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -39067,10 +39072,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>2729</v>
+        <v>322</v>
       </c>
       <c r="O208" t="n">
-        <v>2729</v>
+        <v>322</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -39114,7 +39119,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -39225,7 +39230,7 @@
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
@@ -39262,12 +39267,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -39301,10 +39306,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="O209" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -39376,7 +39381,7 @@
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
@@ -39413,12 +39418,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -39452,10 +39457,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="O210" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -39499,7 +39504,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -39610,7 +39615,7 @@
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
@@ -39647,12 +39652,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39686,10 +39691,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="O211" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -39761,7 +39766,7 @@
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -39798,12 +39803,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39837,10 +39842,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="O212" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -39884,7 +39889,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -39995,7 +40000,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -40032,12 +40037,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -40071,10 +40076,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="O213" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -40146,7 +40151,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -40183,12 +40188,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -40222,10 +40227,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="O214" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
@@ -40269,7 +40274,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -40380,7 +40385,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -40417,12 +40422,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40456,10 +40461,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="O215" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -40531,7 +40536,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -40568,12 +40573,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40607,10 +40612,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="O216" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -40654,7 +40659,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -40765,7 +40770,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -40802,12 +40807,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40841,10 +40846,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="O217" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -40916,7 +40921,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -40953,12 +40958,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40992,10 +40997,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="O218" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -41039,7 +41044,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -41150,7 +41155,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -41187,12 +41192,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -41226,22 +41231,14 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="O219" t="n">
-        <v>196</v>
-      </c>
-      <c r="R219" t="n">
-        <v>3.486465974893709</v>
+        <v>351</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -41256,22 +41253,17 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -41279,47 +41271,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41351,12 +41343,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -41390,29 +41382,29 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="O220" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -41422,7 +41414,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -41437,7 +41429,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -41472,17 +41464,17 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -41495,22 +41487,17 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -41518,47 +41505,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41590,12 +41577,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -41629,13 +41616,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O221" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="R221" t="n">
-        <v>3.891746816750114</v>
+        <v>3.486465974893709</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -41644,7 +41631,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -41664,7 +41651,7 @@
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
@@ -41674,7 +41661,7 @@
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -41682,47 +41669,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41754,12 +41741,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -41793,29 +41780,29 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O222" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -41840,7 +41827,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -41875,17 +41862,17 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -41903,7 +41890,7 @@
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -41913,7 +41900,7 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -41921,47 +41908,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41993,12 +41980,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -42032,13 +42019,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O223" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="R223" t="n">
-        <v>3.551054562747672</v>
+        <v>3.891746816750114</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -42047,7 +42034,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -42077,7 +42064,7 @@
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -42090,42 +42077,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42157,12 +42144,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -42196,29 +42183,29 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O224" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -42243,7 +42230,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -42278,17 +42265,17 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -42316,7 +42303,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -42329,42 +42316,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42396,12 +42383,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -42435,81 +42422,100 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="O225" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="R225" t="n">
-        <v>2.207611762789943</v>
+        <v>3.551054562747672</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42536,17 +42542,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42571,7 +42577,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -42580,81 +42586,175 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>3107</v>
+        <v>380</v>
       </c>
       <c r="O226" t="n">
-        <v>3107</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.890167347851448</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>380</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42686,12 +42786,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42716,7 +42816,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -42725,13 +42825,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="O227" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="R227" t="n">
-        <v>1.245145572501575</v>
+        <v>2.207611762789943</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -42764,42 +42864,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -42861,7 +42961,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -42870,13 +42970,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="O228" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="R228" t="n">
-        <v>1.279812533908085</v>
+        <v>0.890167347851448</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -43006,7 +43106,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -43015,13 +43115,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="O229" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="R229" t="n">
-        <v>1.362039128318566</v>
+        <v>1.245145572501575</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -43121,12 +43221,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43151,25 +43251,22 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>14059</v>
+        <v>4467</v>
       </c>
       <c r="O230" t="n">
-        <v>14059</v>
-      </c>
-      <c r="Q230" t="n">
-        <v>0</v>
+        <v>4467</v>
       </c>
       <c r="R230" t="n">
-        <v>0.9950357289540184</v>
+        <v>1.279812533908085</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43202,42 +43299,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43269,12 +43366,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -43299,109 +43396,90 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>179</v>
+        <v>4754</v>
       </c>
       <c r="O231" t="n">
-        <v>179</v>
+        <v>4754</v>
       </c>
       <c r="R231" t="n">
-        <v>3.184068415846806</v>
+        <v>1.362039128318566</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43428,17 +43506,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43472,175 +43550,84 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>179</v>
+        <v>14059</v>
       </c>
       <c r="O232" t="n">
-        <v>179</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
+        <v>14059</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.9950357289540184</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -43672,12 +43659,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -43711,13 +43698,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="O233" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="R233" t="n">
-        <v>5.130029894806968</v>
+        <v>3.184068415846806</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -43726,7 +43713,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -43746,7 +43733,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -43756,7 +43743,7 @@
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -43764,47 +43751,47 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43836,12 +43823,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -43875,29 +43862,29 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="O234" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -43922,7 +43909,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -43957,17 +43944,17 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -43985,7 +43972,7 @@
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
@@ -43995,7 +43982,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -44003,47 +43990,47 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44075,12 +44062,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44114,13 +44101,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="O235" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="R235" t="n">
-        <v>3.672538008315355</v>
+        <v>5.130029894806968</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -44129,7 +44116,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -44159,7 +44146,7 @@
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
@@ -44172,42 +44159,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44239,12 +44226,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44278,29 +44265,29 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="O236" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -44325,7 +44312,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -44360,17 +44347,17 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -44398,7 +44385,7 @@
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -44411,42 +44398,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44478,12 +44465,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44517,81 +44504,100 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>257</v>
+        <v>393</v>
       </c>
       <c r="O237" t="n">
-        <v>257</v>
+        <v>393</v>
       </c>
       <c r="R237" t="n">
-        <v>1.116842958734282</v>
+        <v>3.672538008315355</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44618,17 +44624,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44662,81 +44668,175 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>5043</v>
+        <v>393</v>
       </c>
       <c r="O238" t="n">
-        <v>5043</v>
-      </c>
-      <c r="R238" t="n">
-        <v>1.444838730355601</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>393</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44768,12 +44868,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44798,7 +44898,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -44807,13 +44907,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>5051</v>
+        <v>257</v>
       </c>
       <c r="O239" t="n">
-        <v>5051</v>
+        <v>257</v>
       </c>
       <c r="R239" t="n">
-        <v>1.447130760861817</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44846,42 +44946,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44943,7 +45043,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -44952,13 +45052,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>4835</v>
+        <v>5043</v>
       </c>
       <c r="O240" t="n">
-        <v>4835</v>
+        <v>5043</v>
       </c>
       <c r="R240" t="n">
-        <v>1.385245937193998</v>
+        <v>1.444838730355601</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -45088,7 +45188,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -45097,13 +45197,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>4565</v>
+        <v>5051</v>
       </c>
       <c r="O241" t="n">
-        <v>4565</v>
+        <v>5051</v>
       </c>
       <c r="R241" t="n">
-        <v>1.307889907609225</v>
+        <v>1.447130760861817</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -45233,7 +45333,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -45242,13 +45342,13 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>5538</v>
+        <v>4835</v>
       </c>
       <c r="O242" t="n">
-        <v>5538</v>
+        <v>4835</v>
       </c>
       <c r="R242" t="n">
-        <v>1.586658117927686</v>
+        <v>1.385245937193998</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -45348,12 +45448,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45378,109 +45478,90 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N243" t="n">
-        <v>45</v>
+        <v>4565</v>
       </c>
       <c r="O243" t="n">
-        <v>45</v>
+        <v>4565</v>
       </c>
       <c r="R243" t="n">
-        <v>0.8004641268888618</v>
+        <v>1.307889907609225</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45507,17 +45588,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45542,184 +45623,90 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>45</v>
+        <v>5538</v>
       </c>
       <c r="O244" t="n">
-        <v>45</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
+        <v>5538</v>
+      </c>
+      <c r="R244" t="n">
+        <v>1.586658117927686</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45751,12 +45738,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45790,13 +45777,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O245" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="R245" t="n">
-        <v>0.9375571876716183</v>
+        <v>0.8004641268888618</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -45805,7 +45792,7 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -45825,7 +45812,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -45835,7 +45822,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -45843,47 +45830,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45915,12 +45902,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -45954,29 +45941,29 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O246" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y246" t="inlineStr">
@@ -46001,7 +45988,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -46036,17 +46023,17 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -46064,7 +46051,7 @@
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
@@ -46074,7 +46061,7 @@
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -46082,47 +46069,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46154,118 +46141,521 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>53</v>
+      </c>
+      <c r="O247" t="n">
+        <v>53</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.9375571876716183</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>53</v>
+      </c>
+      <c r="O248" t="n">
+        <v>53</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G249" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>D033</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>淋病</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="K249" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N247" t="n">
+      <c r="N249" t="n">
         <v>5030</v>
       </c>
-      <c r="O247" t="n">
+      <c r="O249" t="n">
         <v>5030</v>
       </c>
-      <c r="R247" t="n">
+      <c r="R249" t="n">
         <v>1.441114180783001</v>
       </c>
-      <c r="S247" t="inlineStr">
+      <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO247" t="inlineStr">
+      <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP247" t="inlineStr">
+      <c r="AP249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR247" t="inlineStr">
+      <c r="AR249" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS247" t="inlineStr"/>
-      <c r="AT247" t="n">
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="n">
         <v>0</v>
       </c>
-      <c r="AU247" t="inlineStr">
+      <c r="AU249" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV247" t="inlineStr">
+      <c r="AV249" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW247" t="inlineStr">
+      <c r="AW249" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX247" t="inlineStr">
+      <c r="AX249" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY247" t="inlineStr">
+      <c r="AY249" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ247" t="inlineStr">
+      <c r="AZ249" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA247" t="inlineStr">
+      <c r="BA249" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB247" t="inlineStr">
+      <c r="BB249" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC247" t="inlineStr">
+      <c r="BC249" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -46387,7 +46777,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -46397,7 +46787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -46417,7 +46807,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -46449,7 +46839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>283491</v>
+        <v>284745</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -45777,13 +45777,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O245" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R245" t="n">
-        <v>0.8004641268888618</v>
+        <v>0.8894045854320688</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -45941,10 +45941,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O246" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284745</v>
+        <v>284750</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -45777,13 +45777,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O245" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R245" t="n">
-        <v>0.8894045854320688</v>
+        <v>1.156225961061689</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -45941,10 +45941,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O246" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284750</v>
+        <v>284765</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -44504,13 +44504,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O237" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R237" t="n">
-        <v>3.672538008315355</v>
+        <v>3.681882888743638</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44668,10 +44668,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O238" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U238" t="inlineStr">
         <is>
@@ -46180,13 +46180,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="O247" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="R247" t="n">
-        <v>0.9375571876716183</v>
+        <v>1.698216792763686</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -46344,10 +46344,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="O248" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284765</v>
+        <v>284809</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -45777,13 +45777,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="O245" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="R245" t="n">
-        <v>1.156225961061689</v>
+        <v>1.458623520108593</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -45941,10 +45941,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="O246" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284809</v>
+        <v>284826</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -46661,6 +46661,151 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>5079</v>
+      </c>
+      <c r="O250" t="n">
+        <v>5079</v>
+      </c>
+      <c r="R250" t="n">
+        <v>1.455152867633571</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
+      <c r="AT250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46694,7 +46839,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -46777,7 +46922,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -46787,7 +46932,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -46839,7 +46984,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>284826</v>
+        <v>289905</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -45777,13 +45777,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="O245" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="R245" t="n">
-        <v>1.458623520108593</v>
+        <v>2.401392380666586</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -45941,10 +45941,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="O246" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46180,13 +46180,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="O247" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="R247" t="n">
-        <v>1.698216792763686</v>
+        <v>2.72422277172508</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -46344,10 +46344,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="O248" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -46801,6 +46801,151 @@
         </is>
       </c>
       <c r="BC250" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>5862</v>
+      </c>
+      <c r="O251" t="n">
+        <v>5862</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1.679485353429414</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -46839,7 +46984,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -46922,7 +47067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -46932,7 +47077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -46984,7 +47129,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>289905</v>
+        <v>295878</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -39267,12 +39267,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -39306,10 +39306,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>2729</v>
+        <v>534</v>
       </c>
       <c r="O209" t="n">
-        <v>2729</v>
+        <v>534</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
@@ -39418,12 +39418,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -39457,10 +39457,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>2729</v>
+        <v>534</v>
       </c>
       <c r="O210" t="n">
-        <v>2729</v>
+        <v>534</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -39615,7 +39615,7 @@
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
@@ -39652,12 +39652,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39691,10 +39691,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="O211" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -39803,12 +39803,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39842,10 +39842,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="O212" t="n">
-        <v>462</v>
+        <v>2729</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -40037,12 +40037,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -40076,10 +40076,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="O213" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -40188,12 +40188,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -40227,10 +40227,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="O214" t="n">
-        <v>1042</v>
+        <v>462</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -40385,7 +40385,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -40422,12 +40422,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40461,10 +40461,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="O215" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -40573,12 +40573,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40612,10 +40612,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="O216" t="n">
-        <v>170</v>
+        <v>1042</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -40770,7 +40770,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -40807,12 +40807,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40846,10 +40846,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="O217" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -40958,12 +40958,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40997,10 +40997,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="O218" t="n">
-        <v>659</v>
+        <v>170</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -41155,7 +41155,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -41192,12 +41192,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -41231,10 +41231,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="O219" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -41343,12 +41343,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -41382,10 +41382,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="O220" t="n">
-        <v>351</v>
+        <v>659</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -41577,12 +41577,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -41616,22 +41616,14 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="O221" t="n">
-        <v>196</v>
-      </c>
-      <c r="R221" t="n">
-        <v>3.486465974893709</v>
+        <v>351</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -41646,22 +41638,17 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -41669,47 +41656,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41741,12 +41728,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -41780,29 +41767,29 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="O222" t="n">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -41812,7 +41799,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -41827,7 +41814,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -41862,17 +41849,17 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -41885,22 +41872,17 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -41908,47 +41890,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -41980,12 +41962,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -42019,13 +42001,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O223" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="R223" t="n">
-        <v>3.891746816750114</v>
+        <v>3.486465974893709</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -42034,7 +42016,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -42054,7 +42036,7 @@
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
@@ -42064,7 +42046,7 @@
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -42072,47 +42054,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42144,12 +42126,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -42183,29 +42165,29 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O224" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -42230,7 +42212,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -42265,17 +42247,17 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -42293,7 +42275,7 @@
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
@@ -42303,7 +42285,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -42311,47 +42293,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42383,12 +42365,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -42422,13 +42404,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O225" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="R225" t="n">
-        <v>3.551054562747672</v>
+        <v>3.891746816750114</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -42437,7 +42419,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -42467,7 +42449,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -42480,42 +42462,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42547,12 +42529,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42586,29 +42568,29 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O226" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -42633,7 +42615,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -42668,17 +42650,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -42706,7 +42688,7 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -42719,42 +42701,42 @@
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42786,12 +42768,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42825,81 +42807,100 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="O227" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="R227" t="n">
-        <v>2.207611762789943</v>
+        <v>3.551054562747672</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42926,17 +42927,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42961,7 +42962,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -42970,81 +42971,175 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>3107</v>
+        <v>380</v>
       </c>
       <c r="O228" t="n">
-        <v>3107</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.890167347851448</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>380</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43076,12 +43171,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -43106,7 +43201,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -43115,13 +43210,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="O229" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="R229" t="n">
-        <v>1.245145572501575</v>
+        <v>2.207611762789943</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -43154,42 +43249,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43251,7 +43346,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -43260,13 +43355,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="O230" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="R230" t="n">
-        <v>1.279812533908085</v>
+        <v>0.890167347851448</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43396,7 +43491,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -43405,13 +43500,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="O231" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="R231" t="n">
-        <v>1.362039128318566</v>
+        <v>1.245145572501575</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -43511,12 +43606,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43541,25 +43636,22 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>14059</v>
+        <v>4467</v>
       </c>
       <c r="O232" t="n">
-        <v>14059</v>
-      </c>
-      <c r="Q232" t="n">
-        <v>0</v>
+        <v>4467</v>
       </c>
       <c r="R232" t="n">
-        <v>0.9950357289540184</v>
+        <v>1.279812533908085</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -43592,42 +43684,42 @@
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43659,12 +43751,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -43689,109 +43781,90 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>179</v>
+        <v>4754</v>
       </c>
       <c r="O233" t="n">
-        <v>179</v>
+        <v>4754</v>
       </c>
       <c r="R233" t="n">
-        <v>3.184068415846806</v>
+        <v>1.362039128318566</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43818,17 +43891,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -43862,175 +43935,84 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>179</v>
+        <v>14059</v>
       </c>
       <c r="O234" t="n">
-        <v>179</v>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
+        <v>14059</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.9950357289540184</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -44062,12 +44044,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44101,22 +44083,14 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="O235" t="n">
-        <v>290</v>
-      </c>
-      <c r="R235" t="n">
-        <v>5.130029894806968</v>
+        <v>355</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -44131,7 +44105,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
@@ -44139,14 +44113,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT235" t="n">
@@ -44154,47 +44123,47 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44226,12 +44195,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44265,29 +44234,29 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="O236" t="n">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -44297,7 +44266,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -44312,7 +44281,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -44347,17 +44316,17 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -44370,7 +44339,7 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
@@ -44378,14 +44347,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -44393,47 +44357,47 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44465,12 +44429,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44504,22 +44468,14 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>394</v>
+        <v>2823</v>
       </c>
       <c r="O237" t="n">
-        <v>394</v>
-      </c>
-      <c r="R237" t="n">
-        <v>3.681882888743638</v>
+        <v>2823</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -44534,7 +44490,7 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
@@ -44542,14 +44498,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT237" t="n">
@@ -44557,47 +44508,47 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44629,12 +44580,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44668,29 +44619,29 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>394</v>
+        <v>2823</v>
       </c>
       <c r="O238" t="n">
-        <v>394</v>
+        <v>2823</v>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -44700,7 +44651,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -44715,7 +44666,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -44750,17 +44701,17 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -44773,7 +44724,7 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
@@ -44781,14 +44732,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT238" t="n">
@@ -44796,47 +44742,47 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44868,12 +44814,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44907,81 +44853,87 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>257</v>
+        <v>519</v>
       </c>
       <c r="O239" t="n">
-        <v>257</v>
-      </c>
-      <c r="R239" t="n">
-        <v>1.116842958734282</v>
+        <v>519</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45008,17 +44960,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -45052,81 +45004,170 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>5043</v>
+        <v>519</v>
       </c>
       <c r="O240" t="n">
-        <v>5043</v>
-      </c>
-      <c r="R240" t="n">
-        <v>1.444838730355601</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>519</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>1</v>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45158,12 +45199,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45188,7 +45229,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -45197,81 +45238,87 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>5051</v>
+        <v>1020</v>
       </c>
       <c r="O241" t="n">
-        <v>5051</v>
-      </c>
-      <c r="R241" t="n">
-        <v>1.447130760861817</v>
+        <v>1020</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45298,17 +45345,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45333,7 +45380,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -45342,81 +45389,170 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>4835</v>
+        <v>1020</v>
       </c>
       <c r="O242" t="n">
-        <v>4835</v>
-      </c>
-      <c r="R242" t="n">
-        <v>1.385245937193998</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1020</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45448,12 +45584,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45478,7 +45614,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -45487,81 +45623,87 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>4565</v>
+        <v>182</v>
       </c>
       <c r="O243" t="n">
-        <v>4565</v>
-      </c>
-      <c r="R243" t="n">
-        <v>1.307889907609225</v>
+        <v>182</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45588,17 +45730,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45623,7 +45765,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -45632,81 +45774,170 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>5538</v>
+        <v>182</v>
       </c>
       <c r="O244" t="n">
-        <v>5538</v>
-      </c>
-      <c r="R244" t="n">
-        <v>1.586658117927686</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45738,12 +45969,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45768,31 +45999,23 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>135</v>
+        <v>786</v>
       </c>
       <c r="O245" t="n">
-        <v>135</v>
-      </c>
-      <c r="R245" t="n">
-        <v>2.401392380666586</v>
+        <v>786</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -45807,22 +46030,17 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -45830,47 +46048,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45902,12 +46120,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -45932,38 +46150,38 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>135</v>
+        <v>786</v>
       </c>
       <c r="O246" t="n">
-        <v>135</v>
+        <v>786</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y246" t="inlineStr">
@@ -45973,7 +46191,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -45988,7 +46206,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -46023,17 +46241,17 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -46046,22 +46264,17 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -46069,47 +46282,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46141,12 +46354,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46171,31 +46384,23 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>154</v>
+        <v>369</v>
       </c>
       <c r="O247" t="n">
-        <v>154</v>
-      </c>
-      <c r="R247" t="n">
-        <v>2.72422277172508</v>
+        <v>369</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -46210,7 +46415,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
@@ -46218,14 +46423,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -46233,47 +46433,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46305,12 +46505,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46335,38 +46535,38 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>154</v>
+        <v>369</v>
       </c>
       <c r="O248" t="n">
-        <v>154</v>
+        <v>369</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -46376,7 +46576,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46391,7 +46591,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -46426,17 +46626,17 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -46449,7 +46649,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -46457,14 +46657,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -46472,47 +46667,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46544,12 +46739,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46574,90 +46769,109 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N249" t="n">
-        <v>5030</v>
+        <v>179</v>
       </c>
       <c r="O249" t="n">
-        <v>5030</v>
+        <v>179</v>
       </c>
       <c r="R249" t="n">
-        <v>1.441114180783001</v>
+        <v>3.184068415846806</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46684,17 +46898,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46719,90 +46933,184 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N250" t="n">
-        <v>5079</v>
+        <v>179</v>
       </c>
       <c r="O250" t="n">
-        <v>5079</v>
-      </c>
-      <c r="R250" t="n">
-        <v>1.455152867633571</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>179</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46834,118 +47142,2890 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>290</v>
+      </c>
+      <c r="O251" t="n">
+        <v>290</v>
+      </c>
+      <c r="R251" t="n">
+        <v>5.130029894806968</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>290</v>
+      </c>
+      <c r="O252" t="n">
+        <v>290</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>394</v>
+      </c>
+      <c r="O253" t="n">
+        <v>394</v>
+      </c>
+      <c r="R253" t="n">
+        <v>3.681882888743638</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AT253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>394</v>
+      </c>
+      <c r="O254" t="n">
+        <v>394</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>257</v>
+      </c>
+      <c r="O255" t="n">
+        <v>257</v>
+      </c>
+      <c r="R255" t="n">
+        <v>1.116842958734282</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D033</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
         <is>
           <t>淋病</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K256" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>5043</v>
+      </c>
+      <c r="O256" t="n">
+        <v>5043</v>
+      </c>
+      <c r="R256" t="n">
+        <v>1.444838730355601</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>5051</v>
+      </c>
+      <c r="O257" t="n">
+        <v>5051</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1.447130760861817</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>4835</v>
+      </c>
+      <c r="O258" t="n">
+        <v>4835</v>
+      </c>
+      <c r="R258" t="n">
+        <v>1.385245937193998</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>4565</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4565</v>
+      </c>
+      <c r="R259" t="n">
+        <v>1.307889907609225</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
+      <c r="AT259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>5538</v>
+      </c>
+      <c r="O260" t="n">
+        <v>5538</v>
+      </c>
+      <c r="R260" t="n">
+        <v>1.586658117927686</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
+      <c r="AT260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV260" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA260" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB260" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>135</v>
+      </c>
+      <c r="O261" t="n">
+        <v>135</v>
+      </c>
+      <c r="R261" t="n">
+        <v>2.401392380666586</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>135</v>
+      </c>
+      <c r="O262" t="n">
+        <v>135</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>154</v>
+      </c>
+      <c r="O263" t="n">
+        <v>154</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2.72422277172508</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>154</v>
+      </c>
+      <c r="O264" t="n">
+        <v>154</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>5030</v>
+      </c>
+      <c r="O265" t="n">
+        <v>5030</v>
+      </c>
+      <c r="R265" t="n">
+        <v>1.441114180783001</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
+      <c r="AT265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>5079</v>
+      </c>
+      <c r="O266" t="n">
+        <v>5079</v>
+      </c>
+      <c r="R266" t="n">
+        <v>1.455152867633571</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
+      <c r="AT266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M267" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N267" t="n">
         <v>5862</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O267" t="n">
         <v>5862</v>
       </c>
-      <c r="R251" t="n">
+      <c r="R267" t="n">
         <v>1.679485353429414</v>
       </c>
-      <c r="S251" t="inlineStr">
+      <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
+      <c r="AR267" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr"/>
-      <c r="AT251" t="n">
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="n">
         <v>0</v>
       </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AU267" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV267" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW267" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX267" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY267" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ267" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA267" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB267" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC267" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -47067,7 +50147,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -47077,7 +50157,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -47097,7 +50177,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -47129,7 +50209,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>295878</v>
+        <v>302466</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -47584,13 +47584,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O253" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R253" t="n">
-        <v>3.681882888743638</v>
+        <v>3.672538008315355</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -47748,10 +47748,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O254" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
@@ -48857,13 +48857,13 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="O261" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="R261" t="n">
-        <v>2.401392380666586</v>
+        <v>3.23743269097273</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -49021,10 +49021,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="O262" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -50028,6 +50028,554 @@
       <c r="BC267" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>4354</v>
+      </c>
+      <c r="O268" t="n">
+        <v>4354</v>
+      </c>
+      <c r="R268" t="n">
+        <v>1.24743760300779</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50612,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -50147,7 +50695,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -50157,7 +50705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -50177,7 +50725,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -50209,7 +50757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>302466</v>
+        <v>306866</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -42660,7 +42660,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -48857,13 +48857,13 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O261" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="R261" t="n">
-        <v>3.23743269097273</v>
+        <v>3.344161241224579</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -49021,10 +49021,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O262" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -49260,13 +49260,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="O263" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="R263" t="n">
-        <v>2.72422277172508</v>
+        <v>3.874057058492159</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -49424,10 +49424,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="O264" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -50243,13 +50243,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -50407,10 +50407,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>306866</v>
+        <v>306944</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -49637,13 +49637,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O264" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R264" t="n">
-        <v>3.450889791476427</v>
+        <v>3.468677883185068</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -49801,10 +49801,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O265" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -51446,13 +51446,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O274" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="R274" t="n">
-        <v>0.7648879434715791</v>
+        <v>0.9427688605579929</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -51610,10 +51610,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O275" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>314687</v>
+        <v>314698</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R26" t="n">
-        <v>8.450795244687805</v>
+        <v>8.9479008473165</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -36379,13 +36379,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O192" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R192" t="n">
-        <v>8.202242443373459</v>
+        <v>8.699348046002152</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -36543,10 +36543,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O193" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
@@ -42705,12 +42705,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42744,13 +42744,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="O226" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="R226" t="n">
-        <v>3.891746816750114</v>
+        <v>7.456584039430417</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
@@ -42789,55 +42789,55 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -42869,12 +42869,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42908,29 +42908,29 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="O227" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Lekandi</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -42940,7 +42940,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -42955,7 +42955,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -42990,17 +42990,17 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
@@ -43028,55 +43028,55 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -43108,12 +43108,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -43147,13 +43147,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O228" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="R228" t="n">
-        <v>3.551054562747672</v>
+        <v>3.891746816750114</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -43205,42 +43205,42 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43272,12 +43272,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -43311,29 +43311,29 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="O229" t="n">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -43358,7 +43358,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -43393,17 +43393,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -43444,42 +43444,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43511,12 +43511,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43550,81 +43550,100 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="O230" t="n">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="R230" t="n">
-        <v>2.207611762789943</v>
+        <v>3.551054562747672</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43651,17 +43670,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -43686,7 +43705,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -43695,86 +43714,175 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>3107</v>
+        <v>380</v>
       </c>
       <c r="O231" t="n">
-        <v>3107</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0.890167347851448</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>380</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43806,12 +43914,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43836,7 +43944,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -43845,22 +43953,17 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="O232" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="R232" t="n">
-        <v>1.245145572501575</v>
+        <v>2.207611762789943</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -43889,42 +43992,42 @@
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43986,7 +44089,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -43995,13 +44098,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="O233" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="R233" t="n">
-        <v>1.279812533908085</v>
+        <v>0.890167347851448</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -44136,7 +44239,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -44145,13 +44248,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="O234" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="R234" t="n">
-        <v>1.362039128318566</v>
+        <v>1.245145572501575</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -44256,12 +44359,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44286,101 +44389,95 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1128</v>
+        <v>4467</v>
       </c>
       <c r="O235" t="n">
-        <v>1128</v>
+        <v>4467</v>
+      </c>
+      <c r="R235" t="n">
+        <v>1.279812533908085</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44407,17 +44504,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44442,179 +44539,95 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1128</v>
+        <v>4754</v>
       </c>
       <c r="O236" t="n">
-        <v>1128</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Gonorrhoea (All Types)</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>4754</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1.362039128318566</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary gonorrhoea notifications across all reported types; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44646,12 +44659,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44685,20 +44698,19 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>14059</v>
+        <v>1128</v>
       </c>
       <c r="O237" t="n">
-        <v>14059</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0.9950357289540184</v>
+        <v>1128</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -44708,66 +44720,70 @@
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44794,17 +44810,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44838,14 +44854,39 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>355</v>
+        <v>1128</v>
       </c>
       <c r="O238" t="n">
-        <v>355</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>1128</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Gonorrhoea (All Types)</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -44853,6 +44894,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary gonorrhoea notifications across all reported types; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44860,7 +44959,7 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
@@ -44870,55 +44969,55 @@
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44945,17 +45044,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44989,39 +45088,20 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>355</v>
+        <v>14059</v>
       </c>
       <c r="O239" t="n">
-        <v>355</v>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>淋病</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>14059</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0.9950357289540184</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -45029,130 +45109,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45184,12 +45202,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -45223,10 +45241,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2823</v>
+        <v>355</v>
       </c>
       <c r="O240" t="n">
-        <v>2823</v>
+        <v>355</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -45298,7 +45316,7 @@
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
@@ -45335,12 +45353,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45374,10 +45392,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>2823</v>
+        <v>355</v>
       </c>
       <c r="O241" t="n">
-        <v>2823</v>
+        <v>355</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -45421,7 +45439,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -45532,7 +45550,7 @@
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
@@ -45569,12 +45587,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45608,10 +45626,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>519</v>
+        <v>2823</v>
       </c>
       <c r="O242" t="n">
-        <v>519</v>
+        <v>2823</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -45683,7 +45701,7 @@
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
@@ -45720,12 +45738,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45759,10 +45777,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>519</v>
+        <v>2823</v>
       </c>
       <c r="O243" t="n">
-        <v>519</v>
+        <v>2823</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -45806,7 +45824,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -45917,7 +45935,7 @@
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
@@ -45954,12 +45972,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45993,10 +46011,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1020</v>
+        <v>519</v>
       </c>
       <c r="O244" t="n">
-        <v>1020</v>
+        <v>519</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -46068,7 +46086,7 @@
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
@@ -46105,12 +46123,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -46144,10 +46162,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1020</v>
+        <v>519</v>
       </c>
       <c r="O245" t="n">
-        <v>1020</v>
+        <v>519</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46191,7 +46209,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -46302,7 +46320,7 @@
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
@@ -46339,12 +46357,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46378,10 +46396,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>182</v>
+        <v>1020</v>
       </c>
       <c r="O246" t="n">
-        <v>182</v>
+        <v>1020</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -46453,7 +46471,7 @@
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
@@ -46490,12 +46508,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46529,10 +46547,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>182</v>
+        <v>1020</v>
       </c>
       <c r="O247" t="n">
-        <v>182</v>
+        <v>1020</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -46576,7 +46594,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -46687,7 +46705,7 @@
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
@@ -46724,12 +46742,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46763,10 +46781,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>786</v>
+        <v>182</v>
       </c>
       <c r="O248" t="n">
-        <v>786</v>
+        <v>182</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -46838,7 +46856,7 @@
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
@@ -46875,12 +46893,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46914,10 +46932,10 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>786</v>
+        <v>182</v>
       </c>
       <c r="O249" t="n">
-        <v>786</v>
+        <v>182</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
@@ -46961,7 +46979,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -47072,7 +47090,7 @@
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
@@ -47109,12 +47127,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -47148,10 +47166,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>369</v>
+        <v>786</v>
       </c>
       <c r="O250" t="n">
-        <v>369</v>
+        <v>786</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -47223,7 +47241,7 @@
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
@@ -47260,12 +47278,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -47299,10 +47317,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>369</v>
+        <v>786</v>
       </c>
       <c r="O251" t="n">
-        <v>369</v>
+        <v>786</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -47346,7 +47364,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -47457,7 +47475,7 @@
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
@@ -47494,12 +47512,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47533,22 +47551,14 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>179</v>
+        <v>369</v>
       </c>
       <c r="O252" t="n">
-        <v>179</v>
-      </c>
-      <c r="R252" t="n">
-        <v>3.184068415846806</v>
+        <v>369</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47563,22 +47573,17 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT252" t="n">
@@ -47586,47 +47591,47 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47658,12 +47663,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -47697,29 +47702,29 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>179</v>
+        <v>369</v>
       </c>
       <c r="O253" t="n">
-        <v>179</v>
+        <v>369</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="Y253" t="inlineStr">
@@ -47729,7 +47734,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -47744,7 +47749,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -47779,17 +47784,17 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -47802,22 +47807,17 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CN_PROV_DC_GONORRHEA; SER_CN_PROV_REPORT_GONORRHEA</t>
         </is>
       </c>
       <c r="AT253" t="n">
@@ -47825,47 +47825,47 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47897,12 +47897,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -47936,13 +47936,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="O254" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="R254" t="n">
-        <v>5.130029894806968</v>
+        <v>3.184068415846806</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -47971,7 +47971,7 @@
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
@@ -47981,7 +47981,7 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT254" t="n">
@@ -47989,47 +47989,47 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48061,12 +48061,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -48100,29 +48100,29 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="O255" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -48147,7 +48147,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -48182,17 +48182,17 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -48210,7 +48210,7 @@
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
@@ -48220,7 +48220,7 @@
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT255" t="n">
@@ -48228,47 +48228,47 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48300,12 +48300,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -48339,13 +48339,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>393</v>
+        <v>33</v>
       </c>
       <c r="O256" t="n">
-        <v>393</v>
+        <v>33</v>
       </c>
       <c r="R256" t="n">
-        <v>3.672538008315355</v>
+        <v>8.202242443373459</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -48374,7 +48374,7 @@
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
@@ -48384,55 +48384,55 @@
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -48464,12 +48464,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -48503,29 +48503,29 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>393</v>
+        <v>33</v>
       </c>
       <c r="O257" t="n">
-        <v>393</v>
+        <v>33</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Lekandi</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -48550,7 +48550,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -48585,12 +48585,12 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -48613,7 +48613,7 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
@@ -48623,55 +48623,55 @@
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -48703,12 +48703,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -48742,81 +48742,100 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="O258" t="n">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="R258" t="n">
-        <v>1.116842958734282</v>
+        <v>5.130029894806968</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48843,17 +48862,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -48887,86 +48906,175 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>5043</v>
+        <v>290</v>
       </c>
       <c r="O259" t="n">
-        <v>5043</v>
-      </c>
-      <c r="R259" t="n">
-        <v>1.444838730355601</v>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>290</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48998,12 +49106,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -49028,7 +49136,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -49037,86 +49145,100 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>5051</v>
+        <v>393</v>
       </c>
       <c r="O260" t="n">
-        <v>5051</v>
+        <v>393</v>
       </c>
       <c r="R260" t="n">
-        <v>1.447130760861817</v>
+        <v>3.672538008315355</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR260" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -49143,17 +49265,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -49178,7 +49300,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -49187,86 +49309,175 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>4835</v>
+        <v>393</v>
       </c>
       <c r="O261" t="n">
-        <v>4835</v>
-      </c>
-      <c r="R261" t="n">
-        <v>1.385245937193998</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>393</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR261" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -49298,12 +49509,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -49328,7 +49539,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -49337,22 +49548,17 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>4565</v>
+        <v>257</v>
       </c>
       <c r="O262" t="n">
-        <v>4565</v>
+        <v>257</v>
       </c>
       <c r="R262" t="n">
-        <v>1.307889907609225</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -49381,42 +49587,42 @@
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49478,7 +49684,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -49487,13 +49693,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>5538</v>
+        <v>5043</v>
       </c>
       <c r="O263" t="n">
-        <v>5538</v>
+        <v>5043</v>
       </c>
       <c r="R263" t="n">
-        <v>1.586658117927686</v>
+        <v>1.444838730355601</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -49598,12 +49804,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -49628,109 +49834,95 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N264" t="n">
-        <v>195</v>
+        <v>5051</v>
       </c>
       <c r="O264" t="n">
-        <v>195</v>
+        <v>5051</v>
       </c>
       <c r="R264" t="n">
-        <v>3.468677883185068</v>
+        <v>1.447130760861817</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49757,17 +49949,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -49792,184 +49984,95 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N265" t="n">
-        <v>195</v>
+        <v>4835</v>
       </c>
       <c r="O265" t="n">
-        <v>195</v>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>4835</v>
+      </c>
+      <c r="R265" t="n">
+        <v>1.385245937193998</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR265" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -50001,12 +50104,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -50031,109 +50134,95 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>245</v>
+        <v>4565</v>
       </c>
       <c r="O266" t="n">
-        <v>245</v>
+        <v>4565</v>
       </c>
       <c r="R266" t="n">
-        <v>4.33399077319899</v>
+        <v>1.307889907609225</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -50160,17 +50249,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -50195,184 +50284,95 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>245</v>
+        <v>5538</v>
       </c>
       <c r="O267" t="n">
-        <v>245</v>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>5538</v>
+      </c>
+      <c r="R267" t="n">
+        <v>1.586658117927686</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR267" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -50404,12 +50404,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -50443,13 +50443,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="O268" t="n">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="R268" t="n">
-        <v>4.046333225446689</v>
+        <v>3.486465974893709</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -50478,7 +50478,7 @@
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -50496,47 +50496,47 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -50568,12 +50568,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -50607,29 +50607,29 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="O269" t="n">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr">
@@ -50654,7 +50654,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -50689,17 +50689,17 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -50717,7 +50717,7 @@
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
@@ -50727,7 +50727,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -50735,47 +50735,47 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -50846,86 +50846,100 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>5030</v>
+        <v>38</v>
       </c>
       <c r="O270" t="n">
-        <v>5030</v>
+        <v>38</v>
       </c>
       <c r="R270" t="n">
-        <v>1.441114180783001</v>
+        <v>9.445006449945193</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR270" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -50952,17 +50966,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -50987,7 +51001,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -50996,86 +51010,175 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>5079</v>
+        <v>38</v>
       </c>
       <c r="O271" t="n">
-        <v>5079</v>
-      </c>
-      <c r="R271" t="n">
-        <v>1.455152867633571</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>38</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_STI</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Lekandi</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>IS_DOH_sti_current</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -51107,12 +51210,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -51137,7 +51240,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -51146,86 +51249,100 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>5862</v>
+        <v>245</v>
       </c>
       <c r="O272" t="n">
-        <v>5862</v>
+        <v>245</v>
       </c>
       <c r="R272" t="n">
-        <v>1.679485353429414</v>
+        <v>4.33399077319899</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -51252,17 +51369,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -51287,7 +51404,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -51296,86 +51413,175 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>4354</v>
+        <v>245</v>
       </c>
       <c r="O273" t="n">
-        <v>4354</v>
-      </c>
-      <c r="R273" t="n">
-        <v>1.24743760300779</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>245</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -51407,12 +51613,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -51437,22 +51643,22 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N274" t="n">
-        <v>53</v>
+        <v>433</v>
       </c>
       <c r="O274" t="n">
-        <v>53</v>
+        <v>433</v>
       </c>
       <c r="R274" t="n">
-        <v>0.9427688605579929</v>
+        <v>4.046333225446689</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -51461,7 +51667,7 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -51481,7 +51687,7 @@
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr">
@@ -51491,7 +51697,7 @@
       </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
       <c r="AT274" t="n">
@@ -51499,47 +51705,47 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -51571,12 +51777,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -51601,38 +51807,38 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N275" t="n">
-        <v>53</v>
+        <v>433</v>
       </c>
       <c r="O275" t="n">
-        <v>53</v>
+        <v>433</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Gonorré</t>
         </is>
       </c>
       <c r="Y275" t="inlineStr">
@@ -51657,7 +51863,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -51692,17 +51898,17 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -51720,7 +51926,7 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
@@ -51730,7 +51936,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -51738,47 +51944,47 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -51810,12 +52016,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -51840,109 +52046,95 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N276" t="n">
-        <v>34</v>
+        <v>5030</v>
       </c>
       <c r="O276" t="n">
-        <v>34</v>
+        <v>5030</v>
       </c>
       <c r="R276" t="n">
-        <v>0.6014517807704721</v>
+        <v>1.441114180783001</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR276" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr"/>
       <c r="AT276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -51969,17 +52161,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -52004,184 +52196,95 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N277" t="n">
-        <v>34</v>
+        <v>5079</v>
       </c>
       <c r="O277" t="n">
-        <v>34</v>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>5079</v>
+      </c>
+      <c r="R277" t="n">
+        <v>1.455152867633571</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -52243,22 +52346,22 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N278" t="n">
-        <v>5526</v>
+        <v>5862</v>
       </c>
       <c r="O278" t="n">
-        <v>5526</v>
+        <v>5862</v>
       </c>
       <c r="R278" t="n">
-        <v>1.583220072168362</v>
+        <v>1.679485353429414</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -52330,6 +52433,1112 @@
         </is>
       </c>
       <c r="BC278" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>4354</v>
+      </c>
+      <c r="O279" t="n">
+        <v>4354</v>
+      </c>
+      <c r="R279" t="n">
+        <v>1.24743760300779</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>63</v>
+      </c>
+      <c r="O280" t="n">
+        <v>63</v>
+      </c>
+      <c r="R280" t="n">
+        <v>1.120649777644407</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>63</v>
+      </c>
+      <c r="O281" t="n">
+        <v>63</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>93</v>
+      </c>
+      <c r="O282" t="n">
+        <v>93</v>
+      </c>
+      <c r="R282" t="n">
+        <v>1.645147517989821</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>93</v>
+      </c>
+      <c r="O283" t="n">
+        <v>93</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>5526</v>
+      </c>
+      <c r="O284" t="n">
+        <v>5526</v>
+      </c>
+      <c r="R284" t="n">
+        <v>1.583220072168362</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -52451,7 +53660,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -52461,7 +53670,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -52481,7 +53690,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -52513,7 +53722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>314698</v>
+        <v>314873</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O30" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R30" t="n">
-        <v>3.915504899450722</v>
+        <v>3.906160019022439</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O31" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6535,9 +6535,6 @@
       <c r="O32" t="n">
         <v>329</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.09425975456811278</v>
       </c>
@@ -6688,9 +6685,6 @@
       <c r="O33" t="n">
         <v>3425</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.9812755604735145</v>
       </c>
@@ -6841,9 +6835,6 @@
       <c r="O34" t="n">
         <v>4184</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.198731954750711</v>
       </c>
@@ -6994,9 +6985,6 @@
       <c r="O35" t="n">
         <v>4580</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>1.312187464808378</v>
       </c>
@@ -7147,9 +7135,6 @@
       <c r="O36" t="n">
         <v>3880</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.111634795514521</v>
       </c>
@@ -13070,9 +13055,6 @@
       <c r="O67" t="n">
         <v>4416</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>1.265200839430961</v>
       </c>
@@ -13223,9 +13205,6 @@
       <c r="O68" t="n">
         <v>4408</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.262908808924745</v>
       </c>
@@ -13376,9 +13355,6 @@
       <c r="O69" t="n">
         <v>3089</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.8850102792124632</v>
       </c>
@@ -13529,9 +13505,6 @@
       <c r="O70" t="n">
         <v>3461</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.9915896977514842</v>
       </c>
@@ -18659,13 +18632,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O97" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R97" t="n">
-        <v>3.326777432468871</v>
+        <v>3.317432552040588</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18823,10 +18796,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O98" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -19062,16 +19035,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4134</v>
+        <v>4130</v>
       </c>
       <c r="O99" t="n">
-        <v>4134</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
+        <v>4130</v>
       </c>
       <c r="R99" t="n">
-        <v>1.184406764086864</v>
+        <v>1.183260748833756</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -19215,16 +19185,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3715</v>
+        <v>3711</v>
       </c>
       <c r="O100" t="n">
-        <v>3715</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
+        <v>3711</v>
       </c>
       <c r="R100" t="n">
-        <v>1.064361666323827</v>
+        <v>1.063215651070719</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19368,16 +19335,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>4133</v>
+        <v>4125</v>
       </c>
       <c r="O101" t="n">
-        <v>4133</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
+        <v>4125</v>
       </c>
       <c r="R101" t="n">
-        <v>1.184120260273587</v>
+        <v>1.181828229767371</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -19521,16 +19485,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>3646</v>
+        <v>3640</v>
       </c>
       <c r="O102" t="n">
-        <v>3646</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="R102" t="n">
-        <v>1.044592903207718</v>
+        <v>1.042873880328056</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -25059,16 +25020,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="O131" t="n">
-        <v>3124</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
+        <v>3122</v>
       </c>
       <c r="R131" t="n">
-        <v>0.8950379126771559</v>
+        <v>0.8944649050506022</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -25212,16 +25170,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3276</v>
+        <v>3272</v>
       </c>
       <c r="O132" t="n">
-        <v>3276</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
+        <v>3272</v>
       </c>
       <c r="R132" t="n">
-        <v>0.9385864922952506</v>
+        <v>0.9374404770421428</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -25370,9 +25325,6 @@
       <c r="O133" t="n">
         <v>4118</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>1.179822703074433</v>
       </c>
@@ -25518,16 +25470,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>4392</v>
+        <v>4388</v>
       </c>
       <c r="O134" t="n">
-        <v>4392</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
+        <v>4388</v>
       </c>
       <c r="R134" t="n">
-        <v>1.258324747912314</v>
+        <v>1.257178732659206</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -31441,16 +31390,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>4116</v>
+        <v>4112</v>
       </c>
       <c r="O165" t="n">
-        <v>4116</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
+        <v>4112</v>
       </c>
       <c r="R165" t="n">
-        <v>1.179249695447879</v>
+        <v>1.178103680194771</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -31594,16 +31540,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>2792</v>
+        <v>2788</v>
       </c>
       <c r="O166" t="n">
-        <v>2792</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
+        <v>2788</v>
       </c>
       <c r="R166" t="n">
-        <v>0.7999186466692124</v>
+        <v>0.7987726314161047</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -31747,16 +31690,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>4110</v>
+        <v>4105</v>
       </c>
       <c r="O167" t="n">
-        <v>4110</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
+        <v>4105</v>
       </c>
       <c r="R167" t="n">
-        <v>1.177530672568218</v>
+        <v>1.176098153501833</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -31900,16 +31840,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="O168" t="n">
-        <v>869</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="R168" t="n">
-        <v>0.2489718137376596</v>
+        <v>0.2461067756048902</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -43550,13 +43487,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O230" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="R230" t="n">
-        <v>3.551054562747672</v>
+        <v>3.523019921462821</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43714,10 +43651,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O231" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -53539,6 +53476,156 @@
         </is>
       </c>
       <c r="BC284" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>4617</v>
+      </c>
+      <c r="O285" t="n">
+        <v>4617</v>
+      </c>
+      <c r="R285" t="n">
+        <v>1.322788105899625</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr"/>
+      <c r="AT285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -53577,7 +53664,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -53660,7 +53747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -53670,7 +53757,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">
@@ -53722,7 +53809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>314873</v>
+        <v>319430</v>
       </c>
     </row>
     <row r="16">
